--- a/docs/paper/submission_assets/excel/Figure3_run_level_distribution.xlsx
+++ b/docs/paper/submission_assets/excel/Figure3_run_level_distribution.xlsx
@@ -13,14 +13,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RawRuns!$A$1:$L$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Figure!$A$1:$J$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Figure!$A$1:$J$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="83">
   <si>
     <t>variant</t>
   </si>
@@ -260,10 +260,16 @@
 方向相反</t>
   </si>
   <si>
-    <t>图3　运行级分布与尾延迟（原生 Excel 图表组合）</t>
-  </si>
-  <si>
-    <t>两个图表均为可编辑的 Excel 原生图表；各点为独立进程。</t>
+    <t>Panel (a): native category-label helper</t>
+  </si>
+  <si>
+    <t>category_label</t>
+  </si>
+  <si>
+    <t>Panel (b): native metric-label helper</t>
+  </si>
+  <si>
+    <t>metric_label</t>
   </si>
 </sst>
 </file>
@@ -388,34 +394,6 @@
   <c:lang val="en-US"/>
   <c:style val="10"/>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="1" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="111827"/>
-                </a:solidFill>
-                <a:latin typeface="Microsoft YaHei"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="111827"/>
-                </a:solidFill>
-                <a:latin typeface="Microsoft YaHei"/>
-              </a:rPr>
-              <a:t>(a) 进程级 FPS（点：独立进程；横线/误差：均值±样本SD）</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-    </c:title>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -734,6 +712,156 @@
             </c:numRef>
           </c:yVal>
         </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>原生横轴标签</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>DisplayValues!$C$71</c:f>
+                  <c:strCache>
+                    <c:ptCount val="1"/>
+                    <c:pt idx="0">
+                      <c:v>V0</c:v>
+                    </c:pt>
+                  </c:strCache>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="111827"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="b"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>DisplayValues!$C$72</c:f>
+                  <c:strCache>
+                    <c:ptCount val="1"/>
+                    <c:pt idx="0">
+                      <c:v>V2R</c:v>
+                    </c:pt>
+                  </c:strCache>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="111827"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="b"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>DisplayValues!$C$73</c:f>
+                  <c:strCache>
+                    <c:ptCount val="1"/>
+                    <c:pt idx="0">
+                      <c:v>V3R</c:v>
+                    </c:pt>
+                  </c:strCache>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="111827"/>
+                      </a:solidFill>
+                      <a:latin typeface="Times New Roman"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="b"/>
+            </c:dLbl>
+            <c:dLblPos val="b"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>DisplayValues!$A$71:$A$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>DisplayValues!$B$71:$B$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>50.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:scatterChart>
@@ -745,9 +873,37 @@
           <c:min val="0.5"/>
         </c:scaling>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="[=1]&quot;V0&quot;;[=2]&quot;V2R&quot;;&quot;V3R&quot;" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="111827"/>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="900" b="0" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="111827"/>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei"/>
+                  </a:rPr>
+                  <a:t>(a) 进程级 FPS（点：独立进程；横线/误差：均值±样本SD）</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="in"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="none"/>
         <c:spPr>
           <a:ln w="12700">
             <a:solidFill>
@@ -811,7 +967,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -869,34 +1025,6 @@
   <c:lang val="en-US"/>
   <c:style val="10"/>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="1" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="111827"/>
-                </a:solidFill>
-                <a:latin typeface="Microsoft YaHei"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="111827"/>
-                </a:solidFill>
-                <a:latin typeface="Microsoft YaHei"/>
-              </a:rPr>
-              <a:t>(b) 进程级延迟比较（独立进程；横向偏移仅用于区分）</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-    </c:title>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -1172,6 +1300,156 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:v>原生横轴标签</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>DisplayValues!$C$77</c:f>
+                  <c:strCache>
+                    <c:ptCount val="1"/>
+                    <c:pt idx="0">
+                      <c:v>均值</c:v>
+                    </c:pt>
+                  </c:strCache>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="111827"/>
+                      </a:solidFill>
+                      <a:latin typeface="Microsoft YaHei"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="b"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>DisplayValues!$C$78</c:f>
+                  <c:strCache>
+                    <c:ptCount val="1"/>
+                    <c:pt idx="0">
+                      <c:v>P95</c:v>
+                    </c:pt>
+                  </c:strCache>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="111827"/>
+                      </a:solidFill>
+                      <a:latin typeface="Microsoft YaHei"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="b"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout/>
+              <c:tx>
+                <c:strRef>
+                  <c:f>DisplayValues!$C$79</c:f>
+                  <c:strCache>
+                    <c:ptCount val="1"/>
+                    <c:pt idx="0">
+                      <c:v>P99</c:v>
+                    </c:pt>
+                  </c:strCache>
+                </c:strRef>
+              </c:tx>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="111827"/>
+                      </a:solidFill>
+                      <a:latin typeface="Microsoft YaHei"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="b"/>
+            </c:dLbl>
+            <c:dLblPos val="b"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>DisplayValues!$A$77:$A$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>DisplayValues!$B$77:$B$79</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>7.55</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.55</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:v>尾延迟说明</c:v>
           </c:tx>
@@ -1266,9 +1544,37 @@
           <c:min val="0.5"/>
         </c:scaling>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="[=1]&quot;均值&quot;;[=2]&quot;P95&quot;;&quot;P99&quot;" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="111827"/>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="900" b="0" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="111827"/>
+                    </a:solidFill>
+                    <a:latin typeface="Microsoft YaHei"/>
+                  </a:rPr>
+                  <a:t>(b) 进程级延迟比较（独立进程；横向偏移仅用于区分）</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="in"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="none"/>
         <c:spPr>
           <a:ln w="12700">
             <a:solidFill>
@@ -1282,7 +1588,7 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="1000" baseline="0">
-                <a:latin typeface="Microsoft YaHei"/>
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1332,7 +1638,7 @@
           </c:tx>
           <c:layout/>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="in"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1373,6 +1679,10 @@
         <c:idx val="2"/>
         <c:delete val="1"/>
       </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
       <c:layout/>
       <c:txPr>
         <a:bodyPr/>
@@ -1411,13 +1721,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1447,7 +1757,7 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2381,7 +2691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -3293,6 +3603,104 @@
       </c>
       <c r="C66" s="2" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="3">
+        <v>1</v>
+      </c>
+      <c r="B71" s="4">
+        <v>50.5</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="3">
+        <v>2</v>
+      </c>
+      <c r="B72" s="4">
+        <v>50.5</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="3">
+        <v>3</v>
+      </c>
+      <c r="B73" s="4">
+        <v>50.5</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="3">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4">
+        <v>7.55</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="3">
+        <v>2</v>
+      </c>
+      <c r="B78" s="4">
+        <v>7.55</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="3">
+        <v>3</v>
+      </c>
+      <c r="B79" s="4">
+        <v>7.55</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3305,24 +3713,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:B2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
     <col min="2" max="10" width="12.7109375" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="2:2">
-      <c r="B2" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="2" orientation="landscape"/>
   <drawing r:id="rId1"/>

--- a/docs/paper/submission_assets/excel/Figure3_run_level_distribution.xlsx
+++ b/docs/paper/submission_assets/excel/Figure3_run_level_distribution.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RawRuns!$A$1:$L$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Figure!$A$1:$J$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Figure!$A$1:$J$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -395,7 +395,17 @@
   <c:style val="10"/>
   <c:chart>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14999999999999999"/>
+          <c:y val="0.070000000000000007"/>
+          <c:w val="0.80000000000000004"/>
+          <c:h val="0.68000000000000005"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:ser>
@@ -1026,7 +1036,17 @@
   <c:style val="10"/>
   <c:chart>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14999999999999999"/>
+          <c:y val="0.13"/>
+          <c:w val="0.80000000000000004"/>
+          <c:h val="0.59999999999999998"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:ser>
@@ -1527,7 +1547,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>7.55</c:v>
+                  <c:v>7.72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1727,8 +1747,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1751,13 +1771,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3599,7 +3619,7 @@
         <v>2</v>
       </c>
       <c r="B66" s="4">
-        <v>7.55</v>
+        <v>7.72</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>78</v>

--- a/docs/paper/submission_assets/excel/Figure3_run_level_distribution.xlsx
+++ b/docs/paper/submission_assets/excel/Figure3_run_level_distribution.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RawRuns!$A$1:$L$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Figure!$A$1:$J$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Figure!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -400,10 +400,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.14999999999999999"/>
-          <c:y val="0.070000000000000007"/>
-          <c:w val="0.80000000000000004"/>
-          <c:h val="0.68000000000000005"/>
+          <c:x val="0.11"/>
+          <c:y val="0.050000000000000003"/>
+          <c:w val="0.85999999999999999"/>
+          <c:h val="0.72999999999999998"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -909,7 +909,14 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.26000000000000001"/>
+              <c:y val="0.88"/>
+            </c:manualLayout>
+          </c:layout>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="in"/>
@@ -1041,10 +1048,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.14999999999999999"/>
-          <c:y val="0.13"/>
-          <c:w val="0.80000000000000004"/>
-          <c:h val="0.59999999999999998"/>
+          <c:x val="0.11"/>
+          <c:y val="0.11"/>
+          <c:w val="0.85999999999999999"/>
+          <c:h val="0.65000000000000002"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1590,7 +1597,14 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.28000000000000003"/>
+              <c:y val="0.87"/>
+            </c:manualLayout>
+          </c:layout>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="in"/>
@@ -1747,7 +1761,7 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1771,13 +1785,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
